--- a/data/trans_orig/P20D1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>137</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>62,2%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -2211,97 +2211,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14010</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -2667,97 +2667,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>828</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>358</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1749</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -2815,62 +2815,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2689</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>35,4%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>554</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>501</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -4148,97 +4148,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1161</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>11,09%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>479</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>2241</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>11,09%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>2238</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>51,86%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>2685</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>21711</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>46552</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>65831</t>
+          <t>65881</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32390</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>45485</t>
+          <t>45380</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>497</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>985</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>476</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>16380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>70,38%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>722</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,27 +2093,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>816</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>379</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>379</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3075,22 +3075,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>698</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,27 +3266,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,27 +3917,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>540</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>540</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>36025</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46933</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>65833</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>65881</t>
+          <t>75790</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26275</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>45380</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
